--- a/Fusion_omicas/Epi/DMRs_CYP3A5.xlsx
+++ b/Fusion_omicas/Epi/DMRs_CYP3A5.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\ctoma\Fobos\Proyecto_Diana\TFM_GenoStaR\Fusion_omicas\Epi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\Fusion_omicas\Epi\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27135" windowHeight="9660" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19080" windowHeight="8130"/>
   </bookViews>
   <sheets>
     <sheet name="DMPs " sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="115">
   <si>
     <t>CpG</t>
   </si>
@@ -365,7 +365,10 @@
     <t xml:space="preserve">p-valor </t>
   </si>
   <si>
-    <t xml:space="preserve">log p-valor </t>
+    <t xml:space="preserve">log10 p-valor </t>
+  </si>
+  <si>
+    <t>(-LOG10 p-valor)</t>
   </si>
 </sst>
 </file>
@@ -5240,7 +5243,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -5325,103 +5328,103 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B2">
-        <f>LOG(0.763050157368201)</f>
-        <v>-0.11744691374591827</v>
+        <f t="shared" ref="B2:Y2" si="0">-LOG10(B3)</f>
+        <v>0.11744691374591833</v>
       </c>
       <c r="C2">
-        <f>LOG(0.677376008487619)</f>
-        <v>-0.16917018939489578</v>
+        <f t="shared" si="0"/>
+        <v>0.16917018939489606</v>
       </c>
       <c r="D2">
-        <f>LOG(0.446690678177305)</f>
-        <v>-0.34999311056465093</v>
+        <f t="shared" si="0"/>
+        <v>0.34999311056465116</v>
       </c>
       <c r="E2">
-        <f>LOG(0.00154459190416059)</f>
-        <v>-2.8111862458071104</v>
+        <f t="shared" si="0"/>
+        <v>2.8111862458071104</v>
       </c>
       <c r="F2">
-        <f>LOG(0.00349688394456648)</f>
-        <v>-2.456318780922309</v>
+        <f t="shared" si="0"/>
+        <v>2.4563187809223095</v>
       </c>
       <c r="G2" s="2">
-        <f>LOG(0.000232907204500575)</f>
-        <v>-3.63281707725986</v>
+        <f t="shared" si="0"/>
+        <v>3.63281707725986</v>
       </c>
       <c r="H2">
-        <f>LOG(0.00662525152770721)</f>
-        <v>-2.1787976290859974</v>
+        <f t="shared" si="0"/>
+        <v>2.1787976290859974</v>
       </c>
       <c r="I2">
-        <f>LOG(0.032290147646064)</f>
-        <v>-1.4909299691753355</v>
+        <f t="shared" si="0"/>
+        <v>1.4909299691753359</v>
       </c>
       <c r="J2">
-        <f>LOG(0.000990400573963311)</f>
-        <v>-3.0041891166387527</v>
+        <f t="shared" si="0"/>
+        <v>3.0041891166387527</v>
       </c>
       <c r="K2">
-        <f>LOG(0.560480957466666)</f>
-        <v>-0.2514391381227743</v>
+        <f t="shared" si="0"/>
+        <v>0.25143913812277424</v>
       </c>
       <c r="L2">
-        <f>LOG(0.0203663215018036)</f>
-        <v>-1.6910874047618367</v>
+        <f t="shared" si="0"/>
+        <v>1.6910874047618372</v>
       </c>
       <c r="M2">
-        <f>LOG(0.132555155856127)</f>
-        <v>-0.87760337531438248</v>
+        <f t="shared" si="0"/>
+        <v>0.87760337531438182</v>
       </c>
       <c r="N2">
-        <f>LOG(0.74378366429002)</f>
-        <v>-0.12855336427579592</v>
+        <f t="shared" si="0"/>
+        <v>0.12855336427579592</v>
       </c>
       <c r="O2">
-        <f>LOG(0.215001069655738)</f>
-        <v>-0.66755937941263199</v>
+        <f t="shared" si="0"/>
+        <v>0.66755937941263288</v>
       </c>
       <c r="P2" s="2">
-        <f>LOG(3.02565435017965E-06)</f>
-        <v>-5.5191806871468705</v>
+        <f t="shared" si="0"/>
+        <v>5.5191806871468705</v>
       </c>
       <c r="Q2" s="2">
-        <f>LOG(0.000042905682652887)</f>
-        <v>-4.3674851837744733</v>
+        <f t="shared" si="0"/>
+        <v>4.3674851837744733</v>
       </c>
       <c r="R2" s="2">
-        <f>LOG(0.0000721261359958711)</f>
-        <v>-4.1419073335886827</v>
+        <f t="shared" si="0"/>
+        <v>4.1419073335886827</v>
       </c>
       <c r="S2">
-        <f>LOG(0.349895145019742)</f>
-        <v>-0.45606208354099737</v>
+        <f t="shared" si="0"/>
+        <v>0.45606208354099709</v>
       </c>
       <c r="T2">
-        <f>LOG(0.346636686912964)</f>
-        <v>-0.46012547485728977</v>
+        <f t="shared" si="0"/>
+        <v>0.46012547485729005</v>
       </c>
       <c r="U2">
-        <f>LOG(0.99001620507344)</f>
-        <v>-4.3576965980312533E-3</v>
+        <f t="shared" si="0"/>
+        <v>4.3576965980310581E-3</v>
       </c>
       <c r="V2">
-        <f>LOG(0.202093305493189)</f>
-        <v>-0.694448072608008</v>
+        <f t="shared" si="0"/>
+        <v>0.69444807260800778</v>
       </c>
       <c r="W2">
-        <f>LOG(0.532940440218867)</f>
-        <v>-0.27332132367439371</v>
+        <f t="shared" si="0"/>
+        <v>0.27332132367439382</v>
       </c>
       <c r="X2">
-        <f>LOG(0.699551342338508)</f>
-        <v>-0.15518040572393052</v>
+        <f t="shared" si="0"/>
+        <v>0.15518040572393024</v>
       </c>
       <c r="Y2">
-        <f>LOG(0.771758192229898)</f>
-        <v>-0.11251875177608295</v>
+        <f t="shared" si="0"/>
+        <v>0.11251875177608282</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -5499,6 +5502,184 @@
       </c>
       <c r="Y3">
         <v>0.77175819222989828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6">
+        <f t="shared" ref="B6:Y6" si="1">LOG10(B3)</f>
+        <v>-0.11744691374591833</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>-0.16917018939489606</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>-0.34999311056465116</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>-2.8111862458071104</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>-2.4563187809223095</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="1"/>
+        <v>-3.63281707725986</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>-2.1787976290859974</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>-1.4909299691753359</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>-3.0041891166387527</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>-0.25143913812277424</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>-1.6910874047618372</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="1"/>
+        <v>-0.87760337531438182</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="1"/>
+        <v>-0.12855336427579592</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>-0.66755937941263288</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" si="1"/>
+        <v>-5.5191806871468705</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" si="1"/>
+        <v>-4.3674851837744733</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="1"/>
+        <v>-4.1419073335886827</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="1"/>
+        <v>-0.45606208354099709</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="1"/>
+        <v>-0.46012547485729005</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="1"/>
+        <v>-4.3576965980310581E-3</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="1"/>
+        <v>-0.69444807260800778</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="1"/>
+        <v>-0.27332132367439382</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="1"/>
+        <v>-0.15518040572393024</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="1"/>
+        <v>-0.11251875177608282</v>
       </c>
     </row>
   </sheetData>
